--- a/docentes/Cruz Alejo José Armando - Estadisticos 20221.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20221.xlsx
@@ -471,7 +471,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>96.88</v>
+        <v>96.77</v>
       </c>
       <c r="H2">
         <v>8</v>
@@ -588,19 +588,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.77</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -614,16 +617,19 @@
         <v>31</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>31</v>
       </c>
-      <c r="E3">
-        <v>31</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -637,16 +643,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>93.33</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +705,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -705,13 +714,13 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>96.88</v>
+        <v>96.77</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -728,16 +737,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -763,7 +772,7 @@
         <v>93.33</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20221.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -763,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>93.33</v>
+        <v>86.67</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -782,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -812,6 +821,29 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920112</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20221.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20221.xlsx
@@ -841,7 +841,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
